--- a/scenarios/엑셀 결합 데이터.xlsx
+++ b/scenarios/엑셀 결합 데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MCI_Diffusion\MCI_ADV2\scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MCI_ADV\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B7636-E166-441C-AA37-5106C7F57B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4091F1-7AF5-4D25-A5F5-EB43DF1899FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="3375" windowWidth="18810" windowHeight="15345" xr2:uid="{CF92C1C6-8B04-49EC-97E5-D60716126570}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="28800" windowHeight="15345" xr2:uid="{CF92C1C6-8B04-49EC-97E5-D60716126570}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -16071,7 +16071,7 @@
         <v>37.4449939</v>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178">
         <f t="shared" si="2"/>

--- a/scenarios/엑셀 결합 데이터.xlsx
+++ b/scenarios/엑셀 결합 데이터.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="2357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="2364">
   <si>
     <t>전남</t>
   </si>
@@ -7123,6 +7123,27 @@
   </si>
   <si>
     <t>051-709-3000</t>
+  </si>
+  <si>
+    <t>온누리병원_인천서구</t>
+  </si>
+  <si>
+    <t>현대병원_남양주시</t>
+  </si>
+  <si>
+    <t>강병원_포천시</t>
+  </si>
+  <si>
+    <t>강병원_고성군</t>
+  </si>
+  <si>
+    <t>온누리병원_안산단원구</t>
+  </si>
+  <si>
+    <t>현대병원_경주시</t>
+  </si>
+  <si>
+    <t>현대병원_아산시</t>
   </si>
 </sst>
 </file>
@@ -17328,7 +17349,7 @@
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>464</v>
+        <v>2357</v>
       </c>
       <c r="B205">
         <v>11</v>
@@ -25584,7 +25605,7 @@
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>506</v>
+        <v>2358</v>
       </c>
       <c r="B377">
         <v>11</v>
@@ -26304,7 +26325,7 @@
     </row>
     <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>2038</v>
+        <v>2359</v>
       </c>
       <c r="B392">
         <v>21</v>
@@ -26352,7 +26373,7 @@
     </row>
     <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>2038</v>
+        <v>2360</v>
       </c>
       <c r="B393">
         <v>21</v>
@@ -29856,7 +29877,7 @@
     </row>
     <row r="466" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>464</v>
+        <v>2361</v>
       </c>
       <c r="B466">
         <v>21</v>
@@ -33153,10 +33174,10 @@
         <v>6</v>
       </c>
       <c r="L534">
-        <v>128.58190880000001</v>
+        <v>128.0864806</v>
       </c>
       <c r="M534">
-        <v>35.2080609</v>
+        <v>35.0822158</v>
       </c>
       <c r="N534">
         <v>0</v>
@@ -33297,10 +33318,10 @@
         <v>10</v>
       </c>
       <c r="L537">
-        <v>127.10591789999999</v>
+        <v>128.4668345</v>
       </c>
       <c r="M537">
-        <v>37.506115600000001</v>
+        <v>35.856943</v>
       </c>
       <c r="N537">
         <v>0</v>
@@ -33552,7 +33573,7 @@
     </row>
     <row r="543" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>506</v>
+        <v>2362</v>
       </c>
       <c r="B543">
         <v>21</v>
@@ -33585,10 +33606,10 @@
         <v>3</v>
       </c>
       <c r="L543">
-        <v>126.9982627</v>
+        <v>129.2064771</v>
       </c>
       <c r="M543">
-        <v>36.782346199999999</v>
+        <v>35.8450997</v>
       </c>
       <c r="N543">
         <v>0</v>
@@ -33600,7 +33621,7 @@
     </row>
     <row r="544" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>506</v>
+        <v>2363</v>
       </c>
       <c r="B544">
         <v>21</v>
@@ -33633,10 +33654,10 @@
         <v>10</v>
       </c>
       <c r="L544">
-        <v>129.20645759999999</v>
+        <v>126.998274</v>
       </c>
       <c r="M544">
-        <v>35.845100600000002</v>
+        <v>36.7823517</v>
       </c>
       <c r="N544">
         <v>0</v>

--- a/scenarios/엑셀 결합 데이터.xlsx
+++ b/scenarios/엑셀 결합 데이터.xlsx
@@ -10649,8 +10649,10 @@
       <c r="G65" t="s">
         <v>49</v>
       </c>
-      <c r="H65" t="s">
-        <v>1383</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>강원특별자치도 삼척시 오십천로 473</t>
+        </is>
       </c>
       <c r="I65" t="s">
         <v>1384</v>
@@ -10662,10 +10664,10 @@
         <v>20</v>
       </c>
       <c r="L65">
-        <v>129.16380169999999</v>
+        <v>129.1705069</v>
       </c>
       <c r="M65">
-        <v>37.4403018</v>
+        <v>37.4400406</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -18089,8 +18091,10 @@
       <c r="G220" t="s">
         <v>1211</v>
       </c>
-      <c r="H220" t="s">
-        <v>1693</v>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>경상남도 거제시 두모길 16</t>
+        </is>
       </c>
       <c r="I220" t="s">
         <v>1694</v>
@@ -18102,10 +18106,10 @@
         <v>10</v>
       </c>
       <c r="L220">
-        <v>128.7216517</v>
+        <v>128.7221455</v>
       </c>
       <c r="M220">
-        <v>34.871299499999999</v>
+        <v>34.8719559</v>
       </c>
       <c r="N220">
         <v>0</v>
@@ -19254,10 +19258,10 @@
         <v>27</v>
       </c>
       <c r="L244">
-        <v>129.05042839999999</v>
+        <v>129.0500997</v>
       </c>
       <c r="M244">
-        <v>35.157435900000003</v>
+        <v>35.1578852</v>
       </c>
       <c r="N244">
         <v>0</v>
@@ -26105,8 +26109,10 @@
       <c r="G387" t="s">
         <v>144</v>
       </c>
-      <c r="H387" t="s">
-        <v>2028</v>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>부산광역시 기장군 기장읍 대청로72번길 6</t>
+        </is>
       </c>
       <c r="I387" t="s">
         <v>2029</v>
@@ -26118,10 +26124,10 @@
         <v>10</v>
       </c>
       <c r="L387">
-        <v>129.21692110000001</v>
+        <v>129.2164907</v>
       </c>
       <c r="M387">
-        <v>35.235799100000001</v>
+        <v>35.2360312</v>
       </c>
       <c r="N387">
         <v>0</v>
@@ -33174,10 +33180,10 @@
         <v>6</v>
       </c>
       <c r="L534">
-        <v>128.0864806</v>
+        <v>128.0864811</v>
       </c>
       <c r="M534">
-        <v>35.0822158</v>
+        <v>35.0822157</v>
       </c>
       <c r="N534">
         <v>0</v>
@@ -33318,10 +33324,10 @@
         <v>10</v>
       </c>
       <c r="L537">
-        <v>128.4668345</v>
+        <v>128.4668362</v>
       </c>
       <c r="M537">
-        <v>35.856943</v>
+        <v>35.8569413</v>
       </c>
       <c r="N537">
         <v>0</v>
@@ -33606,10 +33612,10 @@
         <v>3</v>
       </c>
       <c r="L543">
-        <v>129.2064771</v>
+        <v>129.2064576</v>
       </c>
       <c r="M543">
-        <v>35.8450997</v>
+        <v>35.8451006</v>
       </c>
       <c r="N543">
         <v>0</v>
@@ -33654,10 +33660,10 @@
         <v>10</v>
       </c>
       <c r="L544">
-        <v>126.998274</v>
+        <v>126.9982627</v>
       </c>
       <c r="M544">
-        <v>36.7823517</v>
+        <v>36.7823462</v>
       </c>
       <c r="N544">
         <v>0</v>
